--- a/ig/nr-update-specialty/StructureDefinition-fr-core-estimated-discharge-date.xlsx
+++ b/ig/nr-update-specialty/StructureDefinition-fr-core-estimated-discharge-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T10:40:37+00:00</t>
+    <t>2024-03-11T10:59:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-update-specialty/StructureDefinition-fr-core-estimated-discharge-date.xlsx
+++ b/ig/nr-update-specialty/StructureDefinition-fr-core-estimated-discharge-date.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-11T10:59:26+00:00</t>
+    <t>2024-03-18T13:00:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
